--- a/backend/data/financials_by_company/1378.HK.xlsx
+++ b/backend/data/financials_by_company/1378.HK.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="cashflow" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="info" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="income" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cashflow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,6 +420,909 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AW6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tax Effect Of Unusual Items</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tax Rate For Calcs</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Normalized EBITDA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Total Unusual Items</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Total Unusual Items Excluding Goodwill</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing Operation Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Reconciled Depreciation</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Reconciled Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>EBIT</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Net Interest Income</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Interest Expense</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Normalized Income</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Net Income From Continuing And Discontinued Operation</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Total Expenses</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Diluted Average Shares</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Basic Average Shares</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Diluted EPS</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Basic EPS</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Diluted NI Availto Com Stockholders</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Average Dilution Earnings</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Net Income Common Stockholders</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Otherunder Preferred Stock Dividend</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Net Income</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Minority Interests</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Net Income Including Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Net Income Continuous Operations</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Tax Provision</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Pretax Income</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Other Non Operating Income Expenses</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Special Income Charges</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>Other Special Charges</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>Write Off</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>Impairment Of Capital Assets</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>Restructuring And Mergern Acquisition</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>Net Non Operating Interest Income Expense</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>Interest Expense Non Operating</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>Interest Income Non Operating</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>Operating Expense</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>Selling General And Administration</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>Selling And Marketing Expense</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>General And Administrative Expense</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Cost Of Revenue</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>Operating Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1285789140.368247</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.269092</v>
+      </c>
+      <c r="D2" t="n">
+        <v>48263044000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-4697827000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-4778245000</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22636105000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>7035572000</v>
+      </c>
+      <c r="I2" t="n">
+        <v>120848476000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>43565217000</v>
+      </c>
+      <c r="K2" t="n">
+        <v>36529645000</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-2201790000</v>
+      </c>
+      <c r="M2" t="n">
+        <v>3483268000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1281478000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>26208978859.63175</v>
+      </c>
+      <c r="P2" t="n">
+        <v>22636105000</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>125162030000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>9494025000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>9494025000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.3842</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.3842</v>
+      </c>
+      <c r="V2" t="n">
+        <v>22636105000</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="n">
+        <v>22636105000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>22636105000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-1517745000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>24153850000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>24153850000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>8892527000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>33046377000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>205893000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-1150162000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-69438000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>722446000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>416736000</v>
+      </c>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>-2201790000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>3483268000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1281478000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>37191695000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4313554000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5018063000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>743466000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4274597000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>41505249000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>120848476000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>162353725000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>162353725000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1216685961.244537</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.251594</v>
+      </c>
+      <c r="D3" t="n">
+        <v>47564484000</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-4835903000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-4835903000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22372331000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6568010000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>114006028000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>42728581000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>36160571000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-2259945000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3363259000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1103314000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>25991548038.75546</v>
+      </c>
+      <c r="P3" t="n">
+        <v>22372331000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>118215019000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>9475538000</v>
+      </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="n">
+        <v>2.3611</v>
+      </c>
+      <c r="V3" t="n">
+        <v>22372331000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>22372331000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>22372331000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>-2173362000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>24545693000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>24545693000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>8251619000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>32797312000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>181002000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>-2798093000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>-100444000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>263058000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>2635479000</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="n">
+        <v>-2259945000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>3363259000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1103314000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>37953701000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>4208991000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5653973000</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>661024000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4992949000</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>42162692000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>114006028000</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>156168720000</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>156168720000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-157541927.697014</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.213506</v>
+      </c>
+      <c r="D4" t="n">
+        <v>27082317000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-737880000</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-737880000</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11460678000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7186035000</v>
+      </c>
+      <c r="I4" t="n">
+        <v>112669035000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>26344437000</v>
+      </c>
+      <c r="K4" t="n">
+        <v>19158402000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-2398120000</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3267938000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>869818000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>12041016072.30299</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11460678000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>115944489000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>9800707000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>9475538000</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.1952</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.2095</v>
+      </c>
+      <c r="V4" t="n">
+        <v>11713440000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>252762000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>11460678000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>11460678000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>-1037074000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>12497752000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>12497752000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3392712000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>15890464000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>154062000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>-842509000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>-90992000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>115104000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>818397000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>-2398120000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>3267938000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>869818000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>17679143000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3275454000</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5708149000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>755274000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4952875000</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>20954597000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>112669035000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>133623632000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>133623632000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-67958551.82445499</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.221915</v>
+      </c>
+      <c r="D5" t="n">
+        <v>22883398000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-306237000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-306237000</v>
+      </c>
+      <c r="G5" t="n">
+        <v>8701953000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6951059000</v>
+      </c>
+      <c r="I5" t="n">
+        <v>113460127000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22577161000</v>
+      </c>
+      <c r="K5" t="n">
+        <v>15626102000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-2461369000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3019544000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>558175000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>8940231448.175545</v>
+      </c>
+      <c r="P5" t="n">
+        <v>8701953000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>116999253000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>9299172000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>9299172000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.9358</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.9358</v>
+      </c>
+      <c r="V5" t="n">
+        <v>8701953000</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8701953000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8701953000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>-1107022000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>9808975000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9808975000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2797583000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>12606558000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>170655000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-264102000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>-22783000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>82569000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>224838000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>-20522000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>-2461369000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>3019544000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>558175000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14700174000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3539126000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>6531438000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>597679000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5933759000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>18239300000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>113460127000</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>131699427000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>131699427000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>44561</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>9070755000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.7119</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>456214000</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="n">
+        <v>-46373000</v>
+      </c>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:BX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1786,7 +2690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2825,7 +3729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3452,212 +4356,212 @@
       </c>
       <c r="DT1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
       <c r="EH1" t="inlineStr">
         <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
           <t>averageAnalystRating</t>
         </is>
       </c>
-      <c r="EI1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="EN1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="EP1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EQ1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="ER1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="ES1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="ET1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EU1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EV1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="EW1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="EX1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="EY1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="EZ1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="FA1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="FB1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>epsCurrentYear</t>
         </is>
       </c>
-      <c r="FC1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FG1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
         </is>
       </c>
       <c r="FJ1" t="inlineStr">
@@ -3682,10 +4586,8 @@
           <t>Zouping</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>256200</t>
-        </is>
+      <c r="D2" t="n">
+        <v>256200</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -3747,7 +4649,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Bo  Zhang', 'age': 56, 'title': 'CEO &amp; Chairman', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 2571740, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Shuliang  Zheng', 'age': 79, 'title': 'Executive Vice Chairperson', 'yearBorn': 1946, 'fiscalYear': 2025, 'totalPay': 1634561, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ruilian  Zhang', 'age': 48, 'title': 'VP, CFO &amp; Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 2289080, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yuting  Wong', 'age': 39, 'title': 'Head of Corporate Finance Department &amp; Executive Director', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 5267433, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yuexia  Zhang', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Bo  Zhang', 'age': 56, 'title': 'CEO &amp; Chairman', 'yearBorn': 1969, 'fiscalYear': 2025, 'totalPay': 2570731, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Shuliang  Zheng', 'age': 79, 'title': 'Executive Vice Chairperson', 'yearBorn': 1946, 'fiscalYear': 2025, 'totalPay': 1633920, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Ruilian  Zhang', 'age': 48, 'title': 'VP, CFO &amp; Executive Director', 'yearBorn': 1977, 'fiscalYear': 2025, 'totalPay': 2288183, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yuting  Wong', 'age': 39, 'title': 'Head of Corporate Finance Department &amp; Executive Director', 'yearBorn': 1986, 'fiscalYear': 2025, 'totalPay': 5265367, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Yuexia  Zhang', 'age': 49, 'title': 'Company Secretary', 'yearBorn': 1976, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -3766,7 +4668,7 @@
         <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="X2" t="n">
         <v>1767139200</v>
@@ -3783,34 +4685,34 @@
         <v>3</v>
       </c>
       <c r="AB2" t="n">
-        <v>28.56</v>
+        <v>26.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>28.88</v>
+        <v>26.78</v>
       </c>
       <c r="AD2" t="n">
-        <v>28.6</v>
+        <v>25.94</v>
       </c>
       <c r="AE2" t="n">
-        <v>29.88</v>
+        <v>27.12</v>
       </c>
       <c r="AF2" t="n">
-        <v>28.56</v>
+        <v>26.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>28.88</v>
+        <v>26.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>28.6</v>
+        <v>25.94</v>
       </c>
       <c r="AI2" t="n">
-        <v>29.88</v>
+        <v>27.12</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.65</v>
       </c>
       <c r="AK2" t="n">
-        <v>5.69</v>
+        <v>6.16</v>
       </c>
       <c r="AL2" t="n">
         <v>1779408000</v>
@@ -3822,34 +4724,34 @@
         <v>7.55</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.914</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.5</v>
+        <v>9.702899</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7.0131674</v>
+        <v>6.481633</v>
       </c>
       <c r="AR2" t="n">
-        <v>44447632</v>
+        <v>38727232</v>
       </c>
       <c r="AS2" t="n">
-        <v>44447632</v>
+        <v>38727232</v>
       </c>
       <c r="AT2" t="n">
-        <v>46485863</v>
+        <v>47658702</v>
       </c>
       <c r="AU2" t="n">
-        <v>45365894</v>
+        <v>59614119</v>
       </c>
       <c r="AV2" t="n">
-        <v>45365894</v>
+        <v>59614119</v>
       </c>
       <c r="AW2" t="n">
-        <v>28.96</v>
+        <v>26.76</v>
       </c>
       <c r="AX2" t="n">
-        <v>29.04</v>
+        <v>26.78</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -3858,13 +4760,13 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>284566159360</v>
+        <v>262963494912</v>
       </c>
       <c r="BB2" t="n">
-        <v>280442002338</v>
+        <v>260410430743</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.02</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
         <v>41.36</v>
@@ -3876,19 +4778,19 @@
         <v>2.88</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.7527541</v>
+        <v>1.6196948</v>
       </c>
       <c r="BH2" t="n">
-        <v>34.3008</v>
+        <v>33.69</v>
       </c>
       <c r="BI2" t="n">
-        <v>32.1152</v>
+        <v>32.211</v>
       </c>
       <c r="BJ2" t="n">
         <v>1.483</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.05192577</v>
+        <v>0.055377148</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -3899,7 +4801,7 @@
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>310421389312</v>
+        <v>288570310656</v>
       </c>
       <c r="BO2" t="n">
         <v>0.13942</v>
@@ -3914,16 +4816,16 @@
         <v>0.62187</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.17756</v>
+        <v>0.17553</v>
       </c>
       <c r="BT2" t="n">
         <v>9819397841</v>
       </c>
       <c r="BU2" t="n">
-        <v>15.461193</v>
+        <v>15.459127</v>
       </c>
       <c r="BV2" t="n">
-        <v>1.8743702</v>
+        <v>1.7323099</v>
       </c>
       <c r="BW2" t="n">
         <v>1767139200</v>
@@ -3944,19 +4846,19 @@
         <v>2.76</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.132227</v>
+        <v>4.131675</v>
       </c>
       <c r="CD2" t="n">
-        <v>1.912</v>
+        <v>1.777</v>
       </c>
       <c r="CE2" t="n">
-        <v>7.309</v>
+        <v>6.794</v>
       </c>
       <c r="CF2" t="n">
-        <v>1.025532</v>
+        <v>0.76184213</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.27294624</v>
+        <v>0.22635591</v>
       </c>
       <c r="CH2" t="n">
         <v>1.65</v>
@@ -3970,19 +4872,19 @@
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>28.98</v>
+        <v>26.78</v>
       </c>
       <c r="CL2" t="n">
-        <v>53.439312</v>
+        <v>53.360886</v>
       </c>
       <c r="CM2" t="n">
-        <v>34.584034</v>
+        <v>34.53328</v>
       </c>
       <c r="CN2" t="n">
-        <v>45.090805</v>
+        <v>44.67605</v>
       </c>
       <c r="CO2" t="n">
-        <v>45.43419</v>
+        <v>45.36751</v>
       </c>
       <c r="CP2" t="n">
         <v>1.47059</v>
@@ -4092,155 +4994,155 @@
       </c>
       <c r="DT2" t="inlineStr">
         <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>CHINAHONGQIAO</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>China Hongqiao Group Limited</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="DU2" t="n">
-        <v>1780387724</v>
-      </c>
-      <c r="DV2" t="inlineStr">
+      <c r="DZ2" t="n">
+        <v>1780992491</v>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DW2" t="inlineStr">
+      <c r="EB2" t="inlineStr">
         <is>
           <t>finmb_118522514</t>
         </is>
       </c>
-      <c r="DX2" t="inlineStr">
+      <c r="EC2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DY2" t="inlineStr">
+      <c r="ED2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EE2" t="n">
         <v>28800000</v>
       </c>
-      <c r="EA2" t="inlineStr">
+      <c r="EF2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="EB2" t="b">
+      <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="EC2" t="n">
-        <v>1.4705886</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>CHINAHONGQIAO</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>China Hongqiao Group Limited</t>
-        </is>
-      </c>
-      <c r="EH2" t="inlineStr">
+      <c r="EH2" t="n">
+        <v>-6.909998</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.20510532</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-5.430998</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.16860694</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EN2" t="inlineStr">
         <is>
           <t>1.5 - Strong Buy</t>
         </is>
       </c>
-      <c r="EI2" t="b">
+      <c r="EO2" t="b">
         <v>0</v>
       </c>
-      <c r="EJ2" t="b">
+      <c r="EP2" t="b">
         <v>0</v>
       </c>
-      <c r="EK2" t="n">
+      <c r="EQ2" t="n">
         <v>1300930200000</v>
       </c>
-      <c r="EL2" t="n">
-        <v>0.42000008</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>28.6 - 29.88</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
+      <c r="ER2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>25.94 - 27.12</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="EO2" t="n">
-        <v>46485863</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>14.959999</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>1.067047</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>14.02 - 41.36</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>-12.380001</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.29932305</v>
-      </c>
       <c r="EU2" t="n">
-        <v>102.5532</v>
+        <v>47658702</v>
       </c>
       <c r="EV2" t="n">
+        <v>12.280001</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>0.8468966</v>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>14.5 - 41.36</t>
+        </is>
+      </c>
+      <c r="EY2" t="n">
+        <v>-14.58</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>-0.3525145</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>76.18420999999999</v>
+      </c>
+      <c r="FB2" t="n">
         <v>1773994200</v>
       </c>
-      <c r="EW2" t="n">
+      <c r="FC2" t="n">
         <v>1773994200</v>
       </c>
-      <c r="EX2" t="n">
+      <c r="FD2" t="n">
         <v>1773994200</v>
       </c>
-      <c r="EY2" t="b">
+      <c r="FE2" t="b">
         <v>0</v>
       </c>
-      <c r="EZ2" t="n">
+      <c r="FF2" t="n">
         <v>2.76</v>
       </c>
-      <c r="FA2" t="n">
-        <v>4.132227</v>
-      </c>
-      <c r="FB2" t="n">
+      <c r="FG2" t="n">
+        <v>4.131675</v>
+      </c>
+      <c r="FH2" t="n">
         <v>3.51902</v>
       </c>
-      <c r="FC2" t="n">
-        <v>8.235246999999999</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>-5.320801</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>-0.15512177</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>-3.1352005</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>-0.09762357000000001</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>15</v>
-      </c>
       <c r="FI2" t="n">
-        <v>15</v>
+        <v>7.610073</v>
       </c>
       <c r="FJ2" t="inlineStr"/>
     </row>
